--- a/docs/4/uifis/Учебный_план_Устройство_и_функционирование_информационной_системы.xlsx
+++ b/docs/4/uifis/Учебный_план_Устройство_и_функционирование_информационной_системы.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D42" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D43" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D44" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D45" s="6">
-        <v>3780</v>
+        <v>84</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
